--- a/Assets/Data/Commodore/VIC-20/250403/Data VIC20 250403 v2.0.0.xlsx
+++ b/Assets/Data/Commodore/VIC-20/250403/Data VIC20 250403 v2.0.0.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.20.10\all\mydir\http\classic-repair-toolbox.dk\public_html\app-data\Data\Commodore\VIC-20\250403\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.20.10\all\mydir\http\classic-repair-toolbox.dk\user-feedback\feedback-EuDEgYYm35Ff8PJc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71AF605B-8A91-4AEF-A7E6-8D73F3E2B71D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD41037C-A271-4495-B398-D5AF0A0B1213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11230" uniqueCount="3130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11227" uniqueCount="3130">
   <si>
     <t>Name</t>
   </si>
@@ -9476,7 +9476,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>2026-July-24</t>
+      <t>2026-July-27</t>
     </r>
   </si>
 </sst>
@@ -10426,6 +10426,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1251FF9-425C-410E-B269-C7726F9C2504}">
   <sheetPr codeName="Sheet2"/>
+  <dimension ref="A1:H156"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12" style="1" customWidth="1"/>
@@ -11594,63 +11595,44 @@
         <v>3008</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R15</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Resistor</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1KΩ</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Resistor</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1KΩ verified. The value found in Commodore's schematic for R15 is incorrect.</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20cd091f-0524-4d10-966c-cf8cd5ebc0e6</t>
-        </is>
+    <row r="72" spans="1:8">
+      <c r="A72" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C72" s="1">
+        <v>6502</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H72" t="s">
+        <v>3059</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>27</v>
+        <v>204</v>
       </c>
       <c r="C73" s="1">
-        <v>6502</v>
+        <v>6561</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H73" t="s">
-        <v>3059</v>
+      <c r="F73" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H73" s="42" t="s">
+        <v>3060</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -11661,47 +11643,41 @@
         <v>204</v>
       </c>
       <c r="C74" s="1">
-        <v>6561</v>
+        <v>6560</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>29</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="H74" s="42" t="s">
-        <v>3060</v>
+        <v>282</v>
+      </c>
+      <c r="H74" t="s">
+        <v>3061</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="1" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>204</v>
+        <v>169</v>
       </c>
       <c r="C75" s="1">
-        <v>6560</v>
+        <v>6522</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F75" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>282</v>
-      </c>
       <c r="H75" t="s">
-        <v>3061</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>169</v>
@@ -11713,47 +11689,56 @@
         <v>29</v>
       </c>
       <c r="H76" t="s">
-        <v>3062</v>
+        <v>3063</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="1" t="s">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>169</v>
+        <v>107</v>
       </c>
       <c r="C77" s="1">
-        <v>6522</v>
+        <v>2364</v>
+      </c>
+      <c r="D77" s="48" t="s">
+        <v>1721</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="G77" s="1" t="s">
+        <v>247</v>
+      </c>
       <c r="H77" t="s">
-        <v>3063</v>
+        <v>3064</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>107</v>
+        <v>213</v>
       </c>
       <c r="C78" s="1">
         <v>2364</v>
       </c>
       <c r="D78" s="48" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="F78" s="1" t="s">
+        <v>278</v>
+      </c>
       <c r="G78" s="1" t="s">
         <v>247</v>
       </c>
       <c r="H78" t="s">
-        <v>3064</v>
+        <v>3065</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -11767,73 +11752,67 @@
         <v>2364</v>
       </c>
       <c r="D79" s="48" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>29</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>247</v>
       </c>
       <c r="H79" t="s">
-        <v>3065</v>
+        <v>3066</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>213</v>
+        <v>35</v>
       </c>
       <c r="C80" s="1">
-        <v>2364</v>
+        <v>2332</v>
       </c>
       <c r="D80" s="48" t="s">
-        <v>1719</v>
+        <v>1722</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F80" s="1" t="s">
-        <v>279</v>
-      </c>
       <c r="G80" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H80" t="s">
-        <v>3066</v>
+        <v>3067</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>35</v>
+        <v>244</v>
       </c>
       <c r="C81" s="1">
-        <v>2332</v>
-      </c>
-      <c r="D81" s="48" t="s">
-        <v>1722</v>
+        <v>2114</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>29</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="H81" t="s">
-        <v>3067</v>
+        <v>3068</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>244</v>
@@ -11848,12 +11827,12 @@
         <v>242</v>
       </c>
       <c r="H82" t="s">
-        <v>3068</v>
+        <v>3069</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="1" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>244</v>
@@ -11868,32 +11847,32 @@
         <v>242</v>
       </c>
       <c r="H83" t="s">
-        <v>3069</v>
+        <v>3070</v>
       </c>
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="1" t="s">
-        <v>196</v>
+        <v>24</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C84" s="1">
-        <v>2114</v>
+        <v>250</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>284</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>29</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="H84" t="s">
-        <v>3070</v>
+        <v>3071</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>250</v>
@@ -11908,100 +11887,97 @@
         <v>249</v>
       </c>
       <c r="H85" t="s">
-        <v>3071</v>
+        <v>3072</v>
       </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="1" t="s">
-        <v>25</v>
+        <v>190</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>284</v>
+        <v>191</v>
+      </c>
+      <c r="C86" s="1">
+        <v>555</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G86" s="1" t="s">
-        <v>249</v>
-      </c>
       <c r="H86" t="s">
-        <v>3072</v>
+        <v>3073</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="1" t="s">
-        <v>190</v>
+        <v>145</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>191</v>
+        <v>248</v>
       </c>
       <c r="C87" s="1">
-        <v>555</v>
+        <v>7402</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H87" t="s">
-        <v>3073</v>
+        <v>3074</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="1" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="C88" s="1">
-        <v>7402</v>
+        <v>142</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>141</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H88" t="s">
-        <v>3074</v>
+        <v>3075</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>142</v>
+        <v>255</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H89" t="s">
-        <v>3075</v>
+        <v>3076</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="1" t="s">
-        <v>138</v>
+        <v>194</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>255</v>
+        <v>188</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>139</v>
+        <v>26</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H90" t="s">
-        <v>3076</v>
+        <v>3077</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="1" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>188</v>
@@ -12013,12 +11989,12 @@
         <v>29</v>
       </c>
       <c r="H91" t="s">
-        <v>3077</v>
+        <v>3078</v>
       </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>188</v>
@@ -12030,100 +12006,100 @@
         <v>29</v>
       </c>
       <c r="H92" t="s">
-        <v>3078</v>
+        <v>3079</v>
       </c>
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="1" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>26</v>
+        <v>95</v>
+      </c>
+      <c r="C93" s="1">
+        <v>4066</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H93" t="s">
-        <v>3079</v>
+        <v>3080</v>
       </c>
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="1" t="s">
-        <v>195</v>
+        <v>143</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C94" s="1">
-        <v>4066</v>
+        <v>253</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="G94" s="1" t="s">
+        <v>165</v>
+      </c>
       <c r="H94" t="s">
-        <v>3080</v>
+        <v>3081</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="1" t="s">
-        <v>143</v>
+        <v>23</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>144</v>
+        <v>28</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G95" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="H95" t="s">
-        <v>3081</v>
+        <v>3082</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="1" t="s">
-        <v>23</v>
+        <v>157</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>28</v>
+        <v>142</v>
+      </c>
+      <c r="C96" s="1">
+        <v>7406</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H96" t="s">
-        <v>3082</v>
+        <v>3083</v>
       </c>
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="1" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C97" s="1">
-        <v>7406</v>
+        <v>135</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>133</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H97" t="s">
-        <v>3083</v>
+        <v>3084</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>135</v>
@@ -12135,12 +12111,12 @@
         <v>29</v>
       </c>
       <c r="H98" t="s">
-        <v>3084</v>
+        <v>3085</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="1" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>135</v>
@@ -12152,29 +12128,26 @@
         <v>29</v>
       </c>
       <c r="H99" t="s">
-        <v>3085</v>
+        <v>3086</v>
       </c>
     </row>
     <row r="100" spans="1:8">
-      <c r="A100" s="1" t="s">
-        <v>132</v>
+      <c r="A100" t="s">
+        <v>2892</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>133</v>
+        <v>2941</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="H100" t="s">
-        <v>3086</v>
+        <v>3009</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" t="s">
-        <v>2892</v>
+        <v>2893</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>2941</v>
@@ -12182,13 +12155,13 @@
       <c r="E101" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H101" t="s">
-        <v>3009</v>
+      <c r="H101" s="1" t="s">
+        <v>3010</v>
       </c>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>2941</v>
@@ -12197,12 +12170,12 @@
         <v>56</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>3010</v>
+        <v>3011</v>
       </c>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" t="s">
-        <v>2894</v>
+        <v>2895</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>2941</v>
@@ -12211,12 +12184,12 @@
         <v>56</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>3011</v>
+        <v>3012</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" t="s">
-        <v>2895</v>
+        <v>2896</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>2941</v>
@@ -12225,12 +12198,12 @@
         <v>56</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>3012</v>
+        <v>3013</v>
       </c>
     </row>
     <row r="105" spans="1:8">
       <c r="A105" t="s">
-        <v>2896</v>
+        <v>2897</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>2941</v>
@@ -12239,12 +12212,12 @@
         <v>56</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>3013</v>
+        <v>3014</v>
       </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106" t="s">
-        <v>2897</v>
+        <v>2898</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>2941</v>
@@ -12253,12 +12226,12 @@
         <v>56</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>3014</v>
+        <v>3015</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" t="s">
-        <v>2898</v>
+        <v>2899</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>2941</v>
@@ -12266,13 +12239,16 @@
       <c r="E107" s="1" t="s">
         <v>56</v>
       </c>
+      <c r="G107" s="1" t="s">
+        <v>3091</v>
+      </c>
       <c r="H107" s="1" t="s">
-        <v>3015</v>
+        <v>3016</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" t="s">
-        <v>2899</v>
+        <v>2900</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>2941</v>
@@ -12280,16 +12256,13 @@
       <c r="E108" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G108" s="1" t="s">
-        <v>3091</v>
-      </c>
       <c r="H108" s="1" t="s">
-        <v>3016</v>
+        <v>3017</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" t="s">
-        <v>2900</v>
+        <v>2901</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>2941</v>
@@ -12298,12 +12271,12 @@
         <v>56</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>3017</v>
+        <v>3018</v>
       </c>
     </row>
     <row r="110" spans="1:8">
       <c r="A110" t="s">
-        <v>2901</v>
+        <v>2902</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>2941</v>
@@ -12312,12 +12285,12 @@
         <v>56</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>3018</v>
+        <v>3019</v>
       </c>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" t="s">
-        <v>2902</v>
+        <v>2903</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>2941</v>
@@ -12325,13 +12298,13 @@
       <c r="E111" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H111" s="1" t="s">
-        <v>3019</v>
+      <c r="H111" s="51" t="s">
+        <v>3020</v>
       </c>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" t="s">
-        <v>2903</v>
+        <v>2904</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>2941</v>
@@ -12339,13 +12312,13 @@
       <c r="E112" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H112" s="51" t="s">
-        <v>3020</v>
+      <c r="H112" s="1" t="s">
+        <v>3021</v>
       </c>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" t="s">
-        <v>2904</v>
+        <v>2905</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>2941</v>
@@ -12354,12 +12327,12 @@
         <v>56</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>3021</v>
+        <v>3022</v>
       </c>
     </row>
     <row r="114" spans="1:8">
       <c r="A114" t="s">
-        <v>2905</v>
+        <v>2906</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>2941</v>
@@ -12368,12 +12341,12 @@
         <v>56</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>3022</v>
+        <v>3023</v>
       </c>
     </row>
     <row r="115" spans="1:8">
       <c r="A115" t="s">
-        <v>2906</v>
+        <v>2907</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>2941</v>
@@ -12382,146 +12355,152 @@
         <v>56</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>3023</v>
+        <v>3024</v>
       </c>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" t="s">
-        <v>2907</v>
+        <v>2908</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>2941</v>
+        <v>2942</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>2943</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>56</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>3024</v>
+        <v>3025</v>
       </c>
     </row>
     <row r="117" spans="1:8">
       <c r="A117" t="s">
-        <v>2908</v>
+        <v>2909</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>2942</v>
+        <v>3120</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>2943</v>
+        <v>3118</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>56</v>
       </c>
+      <c r="G117" s="1" t="s">
+        <v>3096</v>
+      </c>
       <c r="H117" s="1" t="s">
-        <v>3025</v>
+        <v>3026</v>
       </c>
     </row>
     <row r="118" spans="1:8">
       <c r="A118" t="s">
-        <v>2909</v>
+        <v>2910</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>3120</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>3118</v>
+        <v>3119</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G118" s="1" t="s">
-        <v>3096</v>
-      </c>
       <c r="H118" s="1" t="s">
-        <v>3026</v>
+        <v>3027</v>
       </c>
     </row>
     <row r="119" spans="1:8">
       <c r="A119" t="s">
-        <v>2910</v>
+        <v>3092</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>3120</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>3119</v>
+        <v>3117</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>56</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>3027</v>
+        <v>3093</v>
       </c>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" t="s">
-        <v>3092</v>
+        <v>2911</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>3120</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>56</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>3093</v>
+        <v>3028</v>
       </c>
     </row>
     <row r="121" spans="1:8">
-      <c r="A121" t="s">
-        <v>2911</v>
+      <c r="A121" s="1" t="s">
+        <v>178</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>3120</v>
+        <v>179</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>3116</v>
+        <v>180</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>3095</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H121" s="1" t="s">
-        <v>3028</v>
+      <c r="H121" t="s">
+        <v>3087</v>
       </c>
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="1" t="s">
-        <v>178</v>
+        <v>93</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>179</v>
+        <v>94</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>3095</v>
+        <v>106</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>56</v>
       </c>
       <c r="H122" t="s">
-        <v>3087</v>
+        <v>3088</v>
       </c>
     </row>
     <row r="123" spans="1:8">
       <c r="A123" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>56</v>
       </c>
+      <c r="F123" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>285</v>
+      </c>
       <c r="H123" t="s">
-        <v>3088</v>
+        <v>3089</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -12535,38 +12514,35 @@
         <v>56</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H124" t="s">
-        <v>3089</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="125" spans="1:8">
-      <c r="A125" s="1" t="s">
-        <v>90</v>
+      <c r="A125" t="s">
+        <v>2912</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>91</v>
+        <v>2944</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>3102</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F125" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="G125" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="H125" t="s">
-        <v>3090</v>
+        <v>2944</v>
+      </c>
+      <c r="H125" s="1" t="s">
+        <v>3029</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" t="s">
-        <v>2912</v>
+        <v>2913</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>2944</v>
@@ -12578,12 +12554,12 @@
         <v>2944</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>3029</v>
+        <v>3030</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" t="s">
-        <v>2913</v>
+        <v>2914</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>2944</v>
@@ -12595,24 +12571,27 @@
         <v>2944</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>3030</v>
+        <v>3031</v>
       </c>
     </row>
     <row r="128" spans="1:8">
       <c r="A128" t="s">
-        <v>2914</v>
+        <v>2915</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>2944</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>3102</v>
+        <v>3100</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>2944</v>
       </c>
+      <c r="F128" s="1" t="s">
+        <v>278</v>
+      </c>
       <c r="H128" s="1" t="s">
-        <v>3031</v>
+        <v>3032</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -12623,36 +12602,36 @@
         <v>2944</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>3100</v>
+        <v>3101</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>2944</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>3032</v>
+        <v>3121</v>
       </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" t="s">
-        <v>2915</v>
+        <v>2916</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>2944</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>3101</v>
+        <v>3100</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>2944</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>3121</v>
+        <v>3033</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -12663,246 +12642,220 @@
         <v>2944</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>3100</v>
+        <v>3101</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>2944</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>3033</v>
+        <v>3122</v>
       </c>
     </row>
     <row r="132" spans="1:8">
       <c r="A132" t="s">
-        <v>2916</v>
+        <v>2917</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>2944</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>3101</v>
+        <v>3103</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>2944</v>
       </c>
-      <c r="F132" s="1" t="s">
-        <v>279</v>
-      </c>
       <c r="H132" s="1" t="s">
-        <v>3122</v>
+        <v>3034</v>
       </c>
     </row>
     <row r="133" spans="1:8">
       <c r="A133" t="s">
-        <v>2917</v>
+        <v>3128</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>2944</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>3103</v>
+        <v>3104</v>
+      </c>
+      <c r="D133" t="s">
+        <v>3123</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>2944</v>
       </c>
+      <c r="F133" t="s">
+        <v>3123</v>
+      </c>
       <c r="H133" s="1" t="s">
-        <v>3034</v>
+        <v>3035</v>
       </c>
     </row>
     <row r="134" spans="1:8">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R8</t>
-        </is>
-      </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Resistor</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1KΩ</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E134" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Resistor</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1KΩ verified. The value found in Commodore's schematic for R8 is incorrect.</t>
-        </is>
+      <c r="A134" t="s">
+        <v>2918</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>2944</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>3105</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>2944</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>3035</v>
+        <v>3036</v>
       </c>
     </row>
     <row r="135" spans="1:8">
       <c r="A135" t="s">
-        <v>2918</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>2944</v>
+        <v>2919</v>
+      </c>
+      <c r="B135" s="47" t="s">
+        <v>3106</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>3105</v>
+        <v>3104</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>2944</v>
       </c>
+      <c r="G135" s="1" t="s">
+        <v>2945</v>
+      </c>
       <c r="H135" s="1" t="s">
-        <v>3036</v>
+        <v>3037</v>
       </c>
     </row>
     <row r="136" spans="1:8">
       <c r="A136" t="s">
-        <v>2919</v>
-      </c>
-      <c r="B136" s="47" t="s">
-        <v>3106</v>
+        <v>2920</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>2944</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>3104</v>
+        <v>3107</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>2944</v>
       </c>
-      <c r="G136" s="1" t="s">
-        <v>2945</v>
-      </c>
       <c r="H136" s="1" t="s">
-        <v>3037</v>
+        <v>3038</v>
       </c>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" t="s">
-        <v>2920</v>
+        <v>2921</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>2944</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>3107</v>
+        <v>3108</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>2944</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>3038</v>
+        <v>3039</v>
       </c>
     </row>
     <row r="138" spans="1:8">
       <c r="A138" t="s">
-        <v>2921</v>
+        <v>2922</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>2944</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>3108</v>
+        <v>3109</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>2944</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>3039</v>
+        <v>3040</v>
       </c>
     </row>
     <row r="139" spans="1:8">
       <c r="A139" t="s">
-        <v>2922</v>
+        <v>2923</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>2944</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>3109</v>
+        <v>3110</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>2944</v>
       </c>
-      <c r="H139" s="1" t="s">
-        <v>3040</v>
+      <c r="H139" t="s">
+        <v>3041</v>
       </c>
     </row>
     <row r="140" spans="1:8">
       <c r="A140" t="s">
-        <v>2923</v>
+        <v>2924</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>2944</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>3110</v>
+        <v>3104</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>2944</v>
       </c>
+      <c r="G140" t="s">
+        <v>3125</v>
+      </c>
       <c r="H140" t="s">
-        <v>3041</v>
+        <v>3042</v>
       </c>
     </row>
     <row r="141" spans="1:8">
       <c r="A141" t="s">
-        <v>2924</v>
+        <v>2925</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>2944</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>3104</v>
-      </c>
-      <c r="D141" t="s">
-        <v>3123</v>
+        <v>3111</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>2944</v>
       </c>
-      <c r="F141" t="s">
-        <v>3123</v>
-      </c>
-      <c r="G141" t="s">
-        <v>3125</v>
-      </c>
       <c r="H141" t="s">
-        <v>3042</v>
+        <v>3043</v>
       </c>
     </row>
     <row r="142" spans="1:8">
       <c r="A142" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>2944</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>3111</v>
+        <v>3104</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>2944</v>
       </c>
       <c r="H142" t="s">
-        <v>3043</v>
+        <v>3044</v>
       </c>
     </row>
     <row r="143" spans="1:8">
       <c r="A143" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>2944</v>
@@ -12914,12 +12867,12 @@
         <v>2944</v>
       </c>
       <c r="H143" t="s">
-        <v>3044</v>
+        <v>3045</v>
       </c>
     </row>
     <row r="144" spans="1:8">
       <c r="A144" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>2944</v>
@@ -12931,12 +12884,12 @@
         <v>2944</v>
       </c>
       <c r="H144" t="s">
-        <v>3045</v>
+        <v>3046</v>
       </c>
     </row>
     <row r="145" spans="1:8">
       <c r="A145" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>2944</v>
@@ -12948,183 +12901,183 @@
         <v>2944</v>
       </c>
       <c r="H145" t="s">
-        <v>3046</v>
+        <v>3047</v>
       </c>
     </row>
     <row r="146" spans="1:8">
       <c r="A146" t="s">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>2944</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>3104</v>
+        <v>3111</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>2944</v>
       </c>
       <c r="H146" t="s">
-        <v>3047</v>
+        <v>3048</v>
       </c>
     </row>
     <row r="147" spans="1:8">
       <c r="A147" t="s">
-        <v>2930</v>
+        <v>2931</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>2944</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>3111</v>
+        <v>3104</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>2944</v>
       </c>
       <c r="H147" t="s">
-        <v>3048</v>
+        <v>3049</v>
       </c>
     </row>
     <row r="148" spans="1:8">
       <c r="A148" t="s">
-        <v>2931</v>
+        <v>2932</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>2944</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>3104</v>
+        <v>3112</v>
+      </c>
+      <c r="D148" t="s">
+        <v>3123</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>2944</v>
       </c>
+      <c r="F148" t="s">
+        <v>3123</v>
+      </c>
+      <c r="G148" t="s">
+        <v>3126</v>
+      </c>
       <c r="H148" t="s">
-        <v>3049</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="149" spans="1:8">
       <c r="A149" t="s">
-        <v>2932</v>
+        <v>2933</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>2944</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>3112</v>
-      </c>
-      <c r="D149" t="s">
-        <v>3123</v>
+        <v>3113</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>2944</v>
       </c>
-      <c r="F149" t="s">
-        <v>3123</v>
-      </c>
-      <c r="G149" t="s">
-        <v>3126</v>
-      </c>
       <c r="H149" t="s">
-        <v>3050</v>
+        <v>3051</v>
       </c>
     </row>
     <row r="150" spans="1:8">
       <c r="A150" t="s">
-        <v>2933</v>
+        <v>2934</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>2944</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>3113</v>
+        <v>3114</v>
+      </c>
+      <c r="D150" t="s">
+        <v>3123</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>2944</v>
       </c>
+      <c r="F150" t="s">
+        <v>3123</v>
+      </c>
+      <c r="G150" t="s">
+        <v>3127</v>
+      </c>
       <c r="H150" t="s">
-        <v>3051</v>
+        <v>3052</v>
       </c>
     </row>
     <row r="151" spans="1:8">
       <c r="A151" t="s">
-        <v>2934</v>
+        <v>2935</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>2944</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>3114</v>
-      </c>
-      <c r="D151" t="s">
-        <v>3123</v>
+        <v>3104</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>2944</v>
       </c>
-      <c r="F151" t="s">
-        <v>3123</v>
-      </c>
-      <c r="G151" t="s">
-        <v>3127</v>
-      </c>
       <c r="H151" t="s">
-        <v>3052</v>
+        <v>3053</v>
       </c>
     </row>
     <row r="152" spans="1:8">
       <c r="A152" t="s">
-        <v>2935</v>
+        <v>2936</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>2944</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>3104</v>
+        <v>3100</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>2944</v>
       </c>
       <c r="H152" t="s">
-        <v>3053</v>
+        <v>3054</v>
       </c>
     </row>
     <row r="153" spans="1:8">
       <c r="A153" t="s">
-        <v>2936</v>
+        <v>2937</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>2944</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>3100</v>
+        <v>3103</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>2944</v>
       </c>
       <c r="H153" t="s">
-        <v>3054</v>
+        <v>3055</v>
       </c>
     </row>
     <row r="154" spans="1:8">
       <c r="A154" t="s">
-        <v>2937</v>
+        <v>2938</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>2944</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>3103</v>
+        <v>3104</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>2944</v>
       </c>
       <c r="H154" t="s">
-        <v>3055</v>
+        <v>3056</v>
       </c>
     </row>
     <row r="155" spans="1:8">
       <c r="A155" t="s">
-        <v>2938</v>
+        <v>2939</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>2944</v>
@@ -13136,40 +13089,23 @@
         <v>2944</v>
       </c>
       <c r="H155" t="s">
-        <v>3056</v>
+        <v>3057</v>
       </c>
     </row>
     <row r="156" spans="1:8">
       <c r="A156" t="s">
-        <v>2939</v>
+        <v>2940</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>2944</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>3104</v>
+        <v>3115</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>2944</v>
       </c>
       <c r="H156" t="s">
-        <v>3057</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8">
-      <c r="A157" t="s">
-        <v>2940</v>
-      </c>
-      <c r="B157" s="1" t="s">
-        <v>2944</v>
-      </c>
-      <c r="C157" s="1" t="s">
-        <v>3115</v>
-      </c>
-      <c r="E157" s="1" t="s">
-        <v>2944</v>
-      </c>
-      <c r="H157" t="s">
         <v>3058</v>
       </c>
     </row>
@@ -13186,6 +13122,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35D2A4B1-8E0B-46C6-8B83-02048610537D}">
   <sheetPr codeName="Sheet4"/>
+  <dimension ref="A1:K1244"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15" style="1" customWidth="1"/>
@@ -50356,6 +50293,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F00A795-F924-4957-BF24-7CBCF1582012}">
   <sheetPr codeName="Sheet5"/>
+  <dimension ref="A1:D106"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.33203125" customWidth="1"/>
@@ -51062,6 +51000,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9014B11-7294-4050-ABF4-8B4EFBD7F103}">
   <sheetPr codeName="Sheet6"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.33203125" customWidth="1"/>
@@ -51252,6 +51191,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B01DEE13-8567-47C0-98EF-B4590CF5D2FE}">
   <sheetPr codeName="Sheet7"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="24.44140625" customWidth="1"/>
@@ -51481,6 +51421,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{787D0651-AC56-4C79-A3A0-381B16C48D1E}">
   <sheetPr codeName="Sheet8"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="25.6640625" customWidth="1"/>
